--- a/Registro Avance.xlsx
+++ b/Registro Avance.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Julio San Martín\Proyectos\OBSIDIAN_BOVEDA\S26196_DSP_Termografía Emisarios ESVAL y AGUAS DEL VALLE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{509F5404-B39C-47A0-A889-7CA8D8457D48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0370D76E-495A-4878-9899-FA4C498D5597}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C2EFEED4-7A1F-48A9-8656-11DC124AC0D5}"/>
+    <workbookView xWindow="33300" yWindow="2520" windowWidth="21600" windowHeight="11295" xr2:uid="{C2EFEED4-7A1F-48A9-8656-11DC124AC0D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Control avance entregables" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="42">
   <si>
     <t>ID</t>
   </si>
@@ -162,9 +162,6 @@
   </si>
   <si>
     <t>ok</t>
-  </si>
-  <si>
-    <t>Revisar configuracion de vuelo, debe volver a ejecutarse</t>
   </si>
   <si>
     <t>se ocuparon solo las carpetas 2 y 3</t>
@@ -704,7 +701,7 @@
       </c>
       <c r="L2" s="2"/>
     </row>
-    <row r="3" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>1</v>
       </c>
@@ -727,9 +724,7 @@
         <v>1</v>
       </c>
       <c r="H3" s="4"/>
-      <c r="I3" s="3" t="s">
-        <v>41</v>
-      </c>
+      <c r="I3" s="3"/>
       <c r="J3" s="4" t="s">
         <v>40</v>
       </c>
@@ -972,7 +967,7 @@
         <v>3</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>40</v>
